--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\Mexico\Models\eps-mexico\InputData\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92B76C7A-D800-47D5-B312-26DA01D6DC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34DB3AC-854F-4BC5-8BDB-787D4DA2D1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10635" yWindow="2055" windowWidth="24510" windowHeight="17910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>MCF Maximum Capacity Factor</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>Programa de Desarrollo del Sistema Eléctrico Nacional</t>
-  </si>
-  <si>
-    <t>TABLA 4.2.4. FACTOR DE PLANTA</t>
   </si>
   <si>
     <t>Notes</t>
@@ -285,9 +282,6 @@
     <t>Tecnología</t>
   </si>
   <si>
-    <t>Valor medio</t>
-  </si>
-  <si>
     <t>Ciclo combinado (-300 MW)</t>
   </si>
   <si>
@@ -323,6 +317,15 @@
   <si>
     <t xml:space="preserve">geothermal </t>
   </si>
+  <si>
+    <t xml:space="preserve">TABLA 4.2.6. TASAS DE SALIDA FORZADA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa de salida forzada </t>
+  </si>
+  <si>
+    <t>Uptime</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +335,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,7 +519,7 @@
     <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Footnotes: top row" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
@@ -864,7 +867,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
     <col min="2" max="2" width="38.42578125" customWidth="1"/>
@@ -873,15 +876,15 @@
     <col min="8" max="8" width="53.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -891,7 +894,7 @@
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4">
         <v>2024</v>
@@ -899,7 +902,7 @@
       <c r="E4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -907,7 +910,7 @@
       <c r="E5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>4</v>
@@ -915,209 +918,209 @@
       <c r="E6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="9" t="s">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="9" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="9" t="s">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="9" t="s">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="s">
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="9" t="s">
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9" t="s">
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="9"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="9" t="s">
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="9" t="s">
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="9" t="s">
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="9"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="9"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="9"/>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="9"/>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="9"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="9"/>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="B38" s="9" t="s">
+      <c r="C38" s="9"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="C38" s="9"/>
-    </row>
-    <row r="39" spans="2:3">
-      <c r="B39" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="C39" s="9"/>
     </row>
@@ -1134,106 +1137,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C79B55-D4BE-4596-89C4-16553D01BCFE}">
-  <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="B2:D13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <f>6.6</f>
+        <v>6.6</v>
+      </c>
+      <c r="D3">
+        <f>100-C3</f>
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D13" si="0">100-C4</f>
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="2:3">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" t="s">
+      <c r="C5">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="C4">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="B5" t="s">
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>92.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" t="s">
+      <c r="C7">
+        <v>7.1</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>92.9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>13.2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>86.8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>47</v>
       </c>
-      <c r="C6">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" t="s">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>48</v>
       </c>
-      <c r="C7">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" t="s">
+      <c r="C10">
+        <v>11.7</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="C9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" t="s">
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="C10">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" t="s">
+      <c r="C12">
+        <v>6.8</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>51</v>
       </c>
-      <c r="C11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
       <c r="C13">
-        <v>40</v>
+        <v>6.8</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>93.2</v>
       </c>
     </row>
   </sheetData>
@@ -1247,15 +1299,15 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:BN25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" ht="30">
+    <row r="1" spans="1:66" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="5">
         <v>2021</v>
@@ -1408,209 +1460,209 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="C2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="D2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="E2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="F2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="G2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="H2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="I2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="J2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="K2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="L2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="M2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="N2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="O2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="P2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Q2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="R2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="S2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="T2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="U2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="V2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="W2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="X2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Y2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Z2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AA2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AB2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AC2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AD2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AE2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AF2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AG2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AH2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AI2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AJ2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AK2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AL2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AM2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AN2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AO2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AP2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AQ2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AR2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AS2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AT2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AU2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AV2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AW2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AX2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AY2" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="3"/>
@@ -1628,209 +1680,209 @@
       <c r="BM2" s="3"/>
       <c r="BN2" s="3"/>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="C3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="D3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="E3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="F3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="G3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="I3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="J3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="K3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="L3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="M3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="N3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="O3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="P3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Q3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="R3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="S3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="T3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="U3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="V3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="W3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="X3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Y3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Z3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AA3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AB3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AC3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AD3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AE3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AF3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AG3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AH3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AI3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AJ3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AK3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AL3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AM3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AN3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AO3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AP3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AQ3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AR3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AS3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AT3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AU3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AV3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AW3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AX3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AY3" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AZ3" s="3"/>
       <c r="BA3" s="3"/>
@@ -1848,209 +1900,209 @@
       <c r="BM3" s="3"/>
       <c r="BN3" s="3"/>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="C4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="D4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="E4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="F4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="G4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="I4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="J4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="K4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="L4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="M4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="N4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="O4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="P4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Q4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="R4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="S4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="T4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="U4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="V4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="W4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="X4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Y4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Z4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AA4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AB4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AC4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AD4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AE4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AF4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AG4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AH4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AI4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AJ4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AK4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AL4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AM4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AN4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AO4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AP4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AQ4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AR4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AS4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AT4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AU4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AV4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AW4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AX4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AY4" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AZ4" s="3"/>
       <c r="BA4" s="3"/>
@@ -2068,209 +2120,209 @@
       <c r="BM4" s="3"/>
       <c r="BN4" s="3"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="C5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="D5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="E5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="F5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="G5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="H5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="I5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="J5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="K5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="L5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="M5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="N5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="O5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="P5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Q5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="R5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="S5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="T5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="U5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="V5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="W5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="X5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Y5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Z5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AA5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AB5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AC5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AD5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AE5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AF5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AG5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AH5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AI5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AJ5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AK5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AL5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AM5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AN5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AO5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AP5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AQ5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AR5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AS5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AT5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AU5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AV5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AW5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AX5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AY5" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
@@ -2288,9 +2340,9 @@
       <c r="BM5" s="3"/>
       <c r="BN5" s="3"/>
     </row>
-    <row r="6" spans="1:66">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3">
         <v>0.95</v>
@@ -2458,9 +2510,9 @@
       <c r="BM6" s="3"/>
       <c r="BN6" s="3"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -2628,9 +2680,9 @@
       <c r="BM7" s="3"/>
       <c r="BN7" s="3"/>
     </row>
-    <row r="8" spans="1:66">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -2798,9 +2850,9 @@
       <c r="BM8" s="3"/>
       <c r="BN8" s="3"/>
     </row>
-    <row r="9" spans="1:66">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
@@ -2968,9 +3020,9 @@
       <c r="BM9" s="3"/>
       <c r="BN9" s="3"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3">
         <v>0.95</v>
@@ -3138,209 +3190,209 @@
       <c r="BM10" s="3"/>
       <c r="BN10" s="3"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="C11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="D11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="E11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="G11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="H11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="I11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="J11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="K11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="L11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="M11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="N11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="O11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="P11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="Q11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="R11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="S11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="T11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="U11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="V11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="W11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="X11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="Y11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="Z11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AA11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AB11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AC11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AD11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AE11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AF11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AG11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AH11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AI11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AJ11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AK11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AL11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AM11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AN11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AO11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AP11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AQ11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AR11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AS11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AT11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AU11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AV11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AW11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AX11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AY11" s="3">
-        <f>'TABLA 4.2.4'!$C8/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D8/100</f>
+        <v>0.86799999999999999</v>
       </c>
       <c r="AZ11" s="3"/>
       <c r="BA11" s="3"/>
@@ -3358,209 +3410,209 @@
       <c r="BM11" s="3"/>
       <c r="BN11" s="3"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="C12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="D12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="E12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="F12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="G12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="H12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="I12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="J12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="K12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="L12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="M12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="N12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="O12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="P12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Q12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="R12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="S12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="T12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="U12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="V12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="W12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="X12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Y12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Z12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AA12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AB12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AC12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AD12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AE12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AF12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AG12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AH12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AI12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AJ12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AK12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AL12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AM12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AN12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AO12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AP12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AQ12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AR12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AS12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AT12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AU12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AV12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AW12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AX12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AY12" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AZ12" s="3"/>
       <c r="BA12" s="3"/>
@@ -3578,209 +3630,209 @@
       <c r="BM12" s="3"/>
       <c r="BN12" s="3"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="C13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="D13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="E13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="F13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="G13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="I13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="J13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="K13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="L13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="M13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="N13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="O13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="P13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="Q13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="R13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="S13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="T13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="U13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="V13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="W13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="X13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="Y13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="Z13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AA13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AB13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AC13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AD13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AE13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AF13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AG13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AH13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AI13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AJ13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AK13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AL13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AM13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AN13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AO13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AP13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AQ13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AR13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AS13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AT13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AU13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AV13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AW13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AX13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AY13" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C12+'TABLA 4.2.4'!$C13)/200</f>
-        <v>0.52500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D12+'TABLA 4.2.4'!$D13)/200</f>
+        <v>0.93200000000000005</v>
       </c>
       <c r="AZ13" s="3"/>
       <c r="BA13" s="3"/>
@@ -3798,209 +3850,209 @@
       <c r="BM13" s="3"/>
       <c r="BN13" s="3"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="C14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="D14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="E14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="F14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="G14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="H14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="I14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="J14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="K14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="L14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="M14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="N14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="O14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="P14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Q14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="R14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="S14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="T14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="U14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="V14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="W14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="X14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Y14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Z14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AA14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AB14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AC14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AD14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AE14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AF14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AG14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AH14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AI14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AJ14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AK14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AL14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AM14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AN14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AO14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AP14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AQ14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AR14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AS14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AT14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AU14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AV14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AW14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AX14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AY14" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AZ14" s="3"/>
       <c r="BA14" s="3"/>
@@ -4018,9 +4070,9 @@
       <c r="BM14" s="3"/>
       <c r="BN14" s="3"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="3">
         <v>0</v>
@@ -4188,209 +4240,209 @@
       <c r="BM15" s="3"/>
       <c r="BN15" s="3"/>
     </row>
-    <row r="16" spans="1:66">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="C16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="D16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="E16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="F16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="G16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="H16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="I16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="J16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="K16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="L16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="M16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="N16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="O16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="P16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Q16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="R16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="S16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="T16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="U16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="V16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="W16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="X16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Y16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Z16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AA16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AB16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AC16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AD16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AE16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AF16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AG16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AH16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AI16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AJ16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AK16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AL16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AM16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AN16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AO16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AP16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AQ16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AR16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AS16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AT16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AU16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AV16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AW16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AX16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AY16" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AZ16" s="3"/>
       <c r="BA16" s="3"/>
@@ -4408,209 +4460,209 @@
       <c r="BM16" s="3"/>
       <c r="BN16" s="3"/>
     </row>
-    <row r="17" spans="1:66">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="C17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="D17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="E17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="F17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="G17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="H17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="I17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="J17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="K17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="L17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="M17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="N17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="O17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="P17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Q17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="R17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="S17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="T17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="U17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="V17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="W17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="X17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Y17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Z17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AA17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AB17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AC17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AD17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AE17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AF17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AG17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AH17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AI17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AJ17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AK17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AL17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AM17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AN17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AO17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AP17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AQ17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AR17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AS17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AT17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AU17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AV17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AW17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AX17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AY17" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AZ17" s="3"/>
       <c r="BA17" s="3"/>
@@ -4628,9 +4680,9 @@
       <c r="BM17" s="3"/>
       <c r="BN17" s="3"/>
     </row>
-    <row r="18" spans="1:66">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="3">
         <v>0.95</v>
@@ -4798,209 +4850,209 @@
       <c r="BM18" s="3"/>
       <c r="BN18" s="3"/>
     </row>
-    <row r="19" spans="1:66">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="C19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="D19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="E19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="F19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="G19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="H19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="I19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="J19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="K19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="L19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="M19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="N19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="O19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="P19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Q19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="R19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="S19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="T19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="U19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="V19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="W19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="X19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Y19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="Z19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AA19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AB19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AC19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AD19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AE19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AF19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AG19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AH19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AI19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AJ19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AK19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AL19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AM19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AN19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AO19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AP19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AQ19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AR19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AS19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AT19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AU19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AV19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AW19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AX19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AY19" s="3">
-        <f>'TABLA 4.2.4'!$C3/100</f>
-        <v>0.8</v>
+        <f>'TABLA 4.2.4'!$D3/100</f>
+        <v>0.93400000000000005</v>
       </c>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="3"/>
@@ -5018,209 +5070,209 @@
       <c r="BM19" s="3"/>
       <c r="BN19" s="3"/>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="C20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="D20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="E20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="F20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="G20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="I20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="J20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="K20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="L20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="M20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="N20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="O20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="P20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Q20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="R20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="S20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="T20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="U20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="V20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="W20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="X20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Y20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Z20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AA20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AB20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AC20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AD20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AE20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AF20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AG20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AH20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AI20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AJ20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AK20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AL20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AM20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AN20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AO20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AP20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AQ20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AR20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AS20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AT20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AU20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AV20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AW20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AX20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AY20" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AZ20" s="3"/>
       <c r="BA20" s="3"/>
@@ -5238,9 +5290,9 @@
       <c r="BM20" s="3"/>
       <c r="BN20" s="3"/>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3">
         <v>0.95</v>
@@ -5408,209 +5460,209 @@
       <c r="BM21" s="3"/>
       <c r="BN21" s="3"/>
     </row>
-    <row r="22" spans="1:66">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="C22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="D22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="E22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="F22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="G22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="H22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="I22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="J22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="K22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="L22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="M22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="N22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="O22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="P22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Q22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="R22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="S22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="T22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="U22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="V22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="W22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="X22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Y22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="Z22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AA22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AB22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AC22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AD22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AE22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AF22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AG22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AH22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AI22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AJ22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AK22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AL22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AM22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AN22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AO22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AP22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AQ22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AR22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AS22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AT22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AU22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AV22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AW22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AX22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AY22" s="3">
-        <f>'TABLA 4.2.4'!$C11/100</f>
-        <v>0.6</v>
+        <f>'TABLA 4.2.4'!$D11/100</f>
+        <v>0.93299999999999994</v>
       </c>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
@@ -5628,209 +5680,209 @@
       <c r="BM22" s="3"/>
       <c r="BN22" s="3"/>
     </row>
-    <row r="23" spans="1:66">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="C23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="D23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="E23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="F23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="G23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="H23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="I23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="J23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="K23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="L23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="M23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="N23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="O23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="P23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Q23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="R23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="S23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="T23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="U23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="V23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="W23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="X23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Y23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="Z23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AA23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AB23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AC23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AD23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AE23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AF23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AG23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AH23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AI23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AJ23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AK23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AL23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AM23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AN23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AO23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AP23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AQ23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AR23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AS23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AT23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AU23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AV23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AW23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AX23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AY23" s="3">
-        <f>'TABLA 4.2.4'!$C10/100</f>
-        <v>0.9</v>
+        <f>'TABLA 4.2.4'!$D10/100</f>
+        <v>0.88300000000000001</v>
       </c>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="3"/>
@@ -5848,209 +5900,209 @@
       <c r="BM23" s="3"/>
       <c r="BN23" s="3"/>
     </row>
-    <row r="24" spans="1:66">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="C24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="D24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="E24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="F24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="G24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="I24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="J24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="K24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="L24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="M24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="N24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="O24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="P24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Q24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="R24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="S24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="T24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="U24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="V24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="W24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="X24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Y24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="Z24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AA24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AB24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AC24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AD24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AE24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AF24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AG24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AH24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AI24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AJ24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AK24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AL24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AM24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AN24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AO24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AP24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AQ24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AR24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AS24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AT24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AU24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AV24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AW24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AX24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AY24" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C6+'TABLA 4.2.4'!$C7)/200</f>
-        <v>0.7</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D6+'TABLA 4.2.4'!$D7)/200</f>
+        <v>0.92900000000000005</v>
       </c>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="3"/>
@@ -6068,209 +6120,209 @@
       <c r="BM24" s="3"/>
       <c r="BN24" s="3"/>
     </row>
-    <row r="25" spans="1:66">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="C25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="D25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="E25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="F25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="G25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="I25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="J25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="K25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="L25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="M25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="N25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="O25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="P25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Q25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="R25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="S25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="T25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="U25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="V25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="W25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="X25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Y25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="Z25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AA25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AB25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AC25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AD25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AE25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AF25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AG25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AH25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AI25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AJ25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AK25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AL25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AM25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AN25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AO25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AP25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AQ25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AR25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AS25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AT25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AU25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AV25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AW25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AX25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AY25" s="3">
-        <f>AVERAGE('TABLA 4.2.4'!$C4+'TABLA 4.2.4'!$C5)/200</f>
-        <v>0.77500000000000002</v>
+        <f>AVERAGE('TABLA 4.2.4'!$D4+'TABLA 4.2.4'!$D5)/200</f>
+        <v>0.91200000000000003</v>
       </c>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
@@ -6297,21 +6349,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -6455,14 +6492,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D670A5-193B-469D-8425-B8E680B279B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A8AD707-55E2-48C8-9104-478DCA750375}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AA5BCA-E2BD-4EFA-9E83-59B3384404D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6AA5BCA-E2BD-4EFA-9E83-59B3384404D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A8AD707-55E2-48C8-9104-478DCA750375}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D670A5-193B-469D-8425-B8E680B279B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>